--- a/Porte-folio/DDE_Tableau_de_synthese_2026.xlsx
+++ b/Porte-folio/DDE_Tableau_de_synthese_2026.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://siocarriat-my.sharepoint.com/personal/dorian_degotex_sio-carriat_com1/Documents/Porte-folio/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dorian.degotex.BTSSIO-CARRIAT\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="13" documentId="13_ncr:1_{F950EDCB-119F-41D4-BC2C-FF4A792A90A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{48485748-C26B-4B55-B917-4CD4A3F9DFC9}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D25DABD-B63C-4A22-8ABB-DC420A6FFB45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Tableau de synthèse Épreuve E5" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Tableau de synthèse Épreuve E5'!$A$1:$H$35</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Tableau de synthèse Épreuve E5'!$A$1:$H$34</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -187,7 +187,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="_-* #,##0.00\ [$€-1]_-;\-* #,##0.00\ [$€-1]_-;_-* &quot;-&quot;??\ [$€-1]_-"/>
   </numFmts>
-  <fonts count="13" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color theme="1"/>
@@ -226,10 +226,6 @@
     <font>
       <b/>
       <sz val="11"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="16"/>
       <name val="Arial"/>
     </font>
     <font>
@@ -653,7 +649,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="49">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -688,10 +684,7 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -700,10 +693,10 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -712,7 +705,7 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -723,20 +716,68 @@
         </ext>
       </extLst>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -755,54 +796,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1054,7 +1047,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AQ81"/>
+  <dimension ref="A1:AQ80"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="70.42578125" style="1" customWidth="1"/>
@@ -1065,60 +1058,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:43" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="27" t="s">
+      <c r="A1" s="42" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="27"/>
-      <c r="C1" s="27"/>
-      <c r="D1" s="27"/>
-      <c r="E1" s="27"/>
-      <c r="F1" s="27"/>
-      <c r="G1" s="27" t="s">
+      <c r="B1" s="42"/>
+      <c r="C1" s="42"/>
+      <c r="D1" s="42"/>
+      <c r="E1" s="42"/>
+      <c r="F1" s="42"/>
+      <c r="G1" s="42" t="s">
         <v>1</v>
       </c>
-      <c r="H1" s="27"/>
+      <c r="H1" s="42"/>
     </row>
     <row r="2" spans="1:43" ht="41.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="27" t="s">
+      <c r="A2" s="42" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="27"/>
-      <c r="C2" s="27"/>
-      <c r="D2" s="27"/>
-      <c r="E2" s="27"/>
-      <c r="F2" s="27"/>
-      <c r="G2" s="27"/>
-      <c r="H2" s="27"/>
+      <c r="B2" s="42"/>
+      <c r="C2" s="42"/>
+      <c r="D2" s="42"/>
+      <c r="E2" s="42"/>
+      <c r="F2" s="42"/>
+      <c r="G2" s="42"/>
+      <c r="H2" s="42"/>
     </row>
     <row r="3" spans="1:43" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="28" t="s">
+      <c r="A3" s="43" t="s">
         <v>23</v>
       </c>
-      <c r="B3" s="29"/>
-      <c r="C3" s="29"/>
-      <c r="D3" s="29"/>
-      <c r="E3" s="30"/>
-      <c r="F3" s="31" t="s">
+      <c r="B3" s="44"/>
+      <c r="C3" s="44"/>
+      <c r="D3" s="44"/>
+      <c r="E3" s="45"/>
+      <c r="F3" s="46" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="29"/>
-      <c r="H3" s="32"/>
+      <c r="G3" s="44"/>
+      <c r="H3" s="47"/>
       <c r="K3" s="1"/>
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
     </row>
     <row r="4" spans="1:43" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="36" t="s">
+      <c r="A4" s="29" t="s">
         <v>24</v>
       </c>
-      <c r="B4" s="37"/>
-      <c r="C4" s="37"/>
-      <c r="D4" s="37"/>
-      <c r="E4" s="38"/>
+      <c r="B4" s="30"/>
+      <c r="C4" s="30"/>
+      <c r="D4" s="30"/>
+      <c r="E4" s="31"/>
       <c r="F4" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="G4" s="21" t="s">
+      <c r="G4" s="20" t="s">
         <v>25</v>
       </c>
       <c r="H4" s="3" t="s">
@@ -1126,22 +1119,22 @@
       </c>
     </row>
     <row r="5" spans="1:43" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="39" t="s">
+      <c r="A5" s="32" t="s">
         <v>26</v>
       </c>
-      <c r="B5" s="40"/>
-      <c r="C5" s="40"/>
-      <c r="D5" s="40"/>
-      <c r="E5" s="40"/>
-      <c r="F5" s="40"/>
-      <c r="G5" s="40"/>
-      <c r="H5" s="41"/>
+      <c r="B5" s="33"/>
+      <c r="C5" s="33"/>
+      <c r="D5" s="33"/>
+      <c r="E5" s="33"/>
+      <c r="F5" s="33"/>
+      <c r="G5" s="33"/>
+      <c r="H5" s="34"/>
     </row>
     <row r="6" spans="1:43" ht="90" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="42" t="s">
+      <c r="A6" s="35" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="44" t="s">
+      <c r="B6" s="37" t="s">
         <v>7</v>
       </c>
       <c r="C6" s="4" t="s">
@@ -1164,8 +1157,8 @@
       </c>
     </row>
     <row r="7" spans="1:43" s="6" customFormat="1" ht="324.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="43"/>
-      <c r="B7" s="45"/>
+      <c r="A7" s="36"/>
+      <c r="B7" s="38"/>
       <c r="C7" s="7" t="s">
         <v>14</v>
       </c>
@@ -1221,16 +1214,16 @@
       <c r="AQ7"/>
     </row>
     <row r="8" spans="1:43" s="6" customFormat="1" ht="18" x14ac:dyDescent="0.2">
-      <c r="A8" s="46" t="s">
+      <c r="A8" s="39" t="s">
         <v>20</v>
       </c>
-      <c r="B8" s="47"/>
-      <c r="C8" s="47"/>
-      <c r="D8" s="47"/>
-      <c r="E8" s="47"/>
-      <c r="F8" s="47"/>
-      <c r="G8" s="47"/>
-      <c r="H8" s="48"/>
+      <c r="B8" s="40"/>
+      <c r="C8" s="40"/>
+      <c r="D8" s="40"/>
+      <c r="E8" s="40"/>
+      <c r="F8" s="40"/>
+      <c r="G8" s="40"/>
+      <c r="H8" s="41"/>
       <c r="I8"/>
       <c r="J8"/>
       <c r="K8"/>
@@ -1269,21 +1262,21 @@
     </row>
     <row r="9" spans="1:43" s="6" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="9" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="B9" s="10">
-        <v>2025</v>
-      </c>
-      <c r="C9" s="11"/>
-      <c r="D9" s="12"/>
-      <c r="E9" s="12"/>
-      <c r="F9" s="22" t="s">
+        <v>2023</v>
+      </c>
+      <c r="C9" s="21" t="s">
         <v>36</v>
       </c>
-      <c r="G9" s="22" t="s">
+      <c r="D9" s="11"/>
+      <c r="E9" s="11"/>
+      <c r="F9" s="21"/>
+      <c r="G9" s="21" t="s">
         <v>36</v>
       </c>
-      <c r="H9" s="13"/>
+      <c r="H9" s="12"/>
       <c r="I9"/>
       <c r="J9"/>
       <c r="K9"/>
@@ -1322,21 +1315,21 @@
     </row>
     <row r="10" spans="1:43" s="6" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="9" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B10" s="10">
-        <v>2023</v>
-      </c>
-      <c r="C10" s="22" t="s">
+        <v>2024</v>
+      </c>
+      <c r="C10" s="21" t="s">
         <v>36</v>
       </c>
-      <c r="D10" s="12"/>
-      <c r="E10" s="12"/>
-      <c r="F10" s="22"/>
-      <c r="G10" s="22" t="s">
+      <c r="D10" s="11"/>
+      <c r="E10" s="11"/>
+      <c r="F10" s="21"/>
+      <c r="G10" s="21" t="s">
         <v>36</v>
       </c>
-      <c r="H10" s="13"/>
+      <c r="H10" s="12"/>
       <c r="I10"/>
       <c r="J10"/>
       <c r="K10"/>
@@ -1375,21 +1368,17 @@
     </row>
     <row r="11" spans="1:43" s="6" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="9" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B11" s="10">
-        <v>2024</v>
-      </c>
-      <c r="C11" s="22" t="s">
-        <v>36</v>
-      </c>
-      <c r="D11" s="12"/>
-      <c r="E11" s="12"/>
-      <c r="F11" s="22"/>
-      <c r="G11" s="22" t="s">
-        <v>36</v>
-      </c>
-      <c r="H11" s="13"/>
+        <v>2023</v>
+      </c>
+      <c r="C11" s="11"/>
+      <c r="D11" s="11"/>
+      <c r="E11" s="11"/>
+      <c r="F11" s="21"/>
+      <c r="G11" s="21"/>
+      <c r="H11" s="12"/>
       <c r="I11"/>
       <c r="J11"/>
       <c r="K11"/>
@@ -1428,17 +1417,17 @@
     </row>
     <row r="12" spans="1:43" s="6" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="9" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B12" s="10">
-        <v>2023</v>
-      </c>
-      <c r="C12" s="12"/>
-      <c r="D12" s="12"/>
-      <c r="E12" s="12"/>
-      <c r="F12" s="22"/>
-      <c r="G12" s="22"/>
-      <c r="H12" s="13"/>
+        <v>2025</v>
+      </c>
+      <c r="C12" s="22"/>
+      <c r="D12" s="11"/>
+      <c r="E12" s="11"/>
+      <c r="F12" s="21"/>
+      <c r="G12" s="21"/>
+      <c r="H12" s="12"/>
       <c r="I12"/>
       <c r="J12"/>
       <c r="K12"/>
@@ -1477,17 +1466,21 @@
     </row>
     <row r="13" spans="1:43" s="6" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="9" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B13" s="10">
         <v>2025</v>
       </c>
-      <c r="C13" s="23"/>
-      <c r="D13" s="12"/>
-      <c r="E13" s="12"/>
-      <c r="F13" s="22"/>
-      <c r="G13" s="22"/>
-      <c r="H13" s="13"/>
+      <c r="C13" s="21" t="s">
+        <v>36</v>
+      </c>
+      <c r="D13" s="11"/>
+      <c r="E13" s="11"/>
+      <c r="F13" s="21"/>
+      <c r="G13" s="21" t="s">
+        <v>36</v>
+      </c>
+      <c r="H13" s="12"/>
       <c r="I13"/>
       <c r="J13"/>
       <c r="K13"/>
@@ -1526,21 +1519,17 @@
     </row>
     <row r="14" spans="1:43" s="6" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="9" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B14" s="10">
         <v>2025</v>
       </c>
-      <c r="C14" s="22" t="s">
-        <v>36</v>
-      </c>
-      <c r="D14" s="12"/>
-      <c r="E14" s="12"/>
-      <c r="F14" s="22"/>
-      <c r="G14" s="22" t="s">
-        <v>36</v>
-      </c>
-      <c r="H14" s="13"/>
+      <c r="C14" s="11"/>
+      <c r="D14" s="11"/>
+      <c r="E14" s="11"/>
+      <c r="F14" s="21"/>
+      <c r="G14" s="21"/>
+      <c r="H14" s="12"/>
       <c r="I14"/>
       <c r="J14"/>
       <c r="K14"/>
@@ -1579,17 +1568,17 @@
     </row>
     <row r="15" spans="1:43" s="6" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="9" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B15" s="10">
-        <v>2025</v>
-      </c>
-      <c r="C15" s="12"/>
-      <c r="D15" s="12"/>
-      <c r="E15" s="12"/>
-      <c r="F15" s="22"/>
-      <c r="G15" s="22"/>
-      <c r="H15" s="13"/>
+        <v>2024</v>
+      </c>
+      <c r="C15" s="11"/>
+      <c r="D15" s="11"/>
+      <c r="E15" s="11"/>
+      <c r="F15" s="21"/>
+      <c r="G15" s="21"/>
+      <c r="H15" s="12"/>
       <c r="I15"/>
       <c r="J15"/>
       <c r="K15"/>
@@ -1627,18 +1616,22 @@
       <c r="AQ15"/>
     </row>
     <row r="16" spans="1:43" s="6" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="9" t="s">
-        <v>34</v>
+      <c r="A16" s="23" t="s">
+        <v>37</v>
       </c>
       <c r="B16" s="10">
-        <v>2024</v>
-      </c>
-      <c r="C16" s="12"/>
-      <c r="D16" s="12"/>
-      <c r="E16" s="12"/>
-      <c r="F16" s="22"/>
-      <c r="G16" s="22"/>
-      <c r="H16" s="13"/>
+        <v>2026</v>
+      </c>
+      <c r="C16" s="21"/>
+      <c r="D16" s="21"/>
+      <c r="E16" s="21" t="s">
+        <v>36</v>
+      </c>
+      <c r="F16" s="21"/>
+      <c r="G16" s="21"/>
+      <c r="H16" s="24" t="s">
+        <v>36</v>
+      </c>
       <c r="I16"/>
       <c r="J16"/>
       <c r="K16"/>
@@ -1676,20 +1669,28 @@
       <c r="AQ16"/>
     </row>
     <row r="17" spans="1:43" s="6" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="24" t="s">
-        <v>37</v>
-      </c>
-      <c r="B17" s="10">
-        <v>2026</v>
-      </c>
-      <c r="C17" s="22"/>
-      <c r="D17" s="22"/>
-      <c r="E17" s="22" t="s">
+      <c r="A17" s="25" t="s">
+        <v>38</v>
+      </c>
+      <c r="B17" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="C17" s="21" t="s">
         <v>36</v>
       </c>
-      <c r="F17" s="22"/>
-      <c r="G17" s="22"/>
-      <c r="H17" s="25" t="s">
+      <c r="D17" s="21" t="s">
+        <v>36</v>
+      </c>
+      <c r="E17" s="21" t="s">
+        <v>36</v>
+      </c>
+      <c r="F17" s="21" t="s">
+        <v>36</v>
+      </c>
+      <c r="G17" s="21" t="s">
+        <v>36</v>
+      </c>
+      <c r="H17" s="24" t="s">
         <v>36</v>
       </c>
       <c r="I17"/>
@@ -1728,31 +1729,17 @@
       <c r="AP17"/>
       <c r="AQ17"/>
     </row>
-    <row r="18" spans="1:43" s="6" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:43" s="6" customFormat="1" ht="18" x14ac:dyDescent="0.2">
       <c r="A18" s="26" t="s">
-        <v>38</v>
-      </c>
-      <c r="B18" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="C18" s="22" t="s">
-        <v>36</v>
-      </c>
-      <c r="D18" s="22" t="s">
-        <v>36</v>
-      </c>
-      <c r="E18" s="22" t="s">
-        <v>36</v>
-      </c>
-      <c r="F18" s="22" t="s">
-        <v>36</v>
-      </c>
-      <c r="G18" s="22" t="s">
-        <v>36</v>
-      </c>
-      <c r="H18" s="25" t="s">
-        <v>36</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="B18" s="27"/>
+      <c r="C18" s="27"/>
+      <c r="D18" s="27"/>
+      <c r="E18" s="27"/>
+      <c r="F18" s="27"/>
+      <c r="G18" s="27"/>
+      <c r="H18" s="28"/>
       <c r="I18"/>
       <c r="J18"/>
       <c r="K18"/>
@@ -1789,17 +1776,21 @@
       <c r="AP18"/>
       <c r="AQ18"/>
     </row>
-    <row r="19" spans="1:43" s="6" customFormat="1" ht="18" x14ac:dyDescent="0.2">
-      <c r="A19" s="33" t="s">
-        <v>21</v>
-      </c>
-      <c r="B19" s="34"/>
-      <c r="C19" s="34"/>
-      <c r="D19" s="34"/>
-      <c r="E19" s="34"/>
-      <c r="F19" s="34"/>
-      <c r="G19" s="34"/>
-      <c r="H19" s="35"/>
+    <row r="19" spans="1:43" s="6" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="B19" s="10">
+        <v>2025</v>
+      </c>
+      <c r="C19" s="11"/>
+      <c r="D19" s="11"/>
+      <c r="E19" s="11"/>
+      <c r="F19" s="21"/>
+      <c r="G19" s="21" t="s">
+        <v>36</v>
+      </c>
+      <c r="H19" s="12"/>
       <c r="I19"/>
       <c r="J19"/>
       <c r="K19"/>
@@ -1838,19 +1829,21 @@
     </row>
     <row r="20" spans="1:43" s="6" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="9" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="B20" s="10">
         <v>2025</v>
       </c>
-      <c r="C20" s="12"/>
-      <c r="D20" s="12"/>
-      <c r="E20" s="12"/>
-      <c r="F20" s="22"/>
-      <c r="G20" s="22" t="s">
+      <c r="C20" s="11"/>
+      <c r="D20" s="11"/>
+      <c r="E20" s="11"/>
+      <c r="F20" s="21" t="s">
         <v>36</v>
       </c>
-      <c r="H20" s="13"/>
+      <c r="G20" s="21" t="s">
+        <v>36</v>
+      </c>
+      <c r="H20" s="12"/>
       <c r="I20"/>
       <c r="J20"/>
       <c r="K20"/>
@@ -1888,14 +1881,13 @@
       <c r="AQ20"/>
     </row>
     <row r="21" spans="1:43" s="6" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="9"/>
       <c r="B21" s="10"/>
-      <c r="C21" s="12"/>
-      <c r="D21" s="12"/>
-      <c r="E21" s="12"/>
-      <c r="F21" s="12"/>
-      <c r="G21" s="12"/>
-      <c r="H21" s="13"/>
+      <c r="C21" s="11"/>
+      <c r="D21" s="11"/>
+      <c r="E21" s="11"/>
+      <c r="F21" s="11"/>
+      <c r="G21" s="11"/>
+      <c r="H21" s="12"/>
       <c r="I21"/>
       <c r="J21"/>
       <c r="K21"/>
@@ -1935,12 +1927,12 @@
     <row r="22" spans="1:43" s="6" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="9"/>
       <c r="B22" s="10"/>
-      <c r="C22" s="12"/>
-      <c r="D22" s="12"/>
-      <c r="E22" s="12"/>
-      <c r="F22" s="12"/>
-      <c r="G22" s="12"/>
-      <c r="H22" s="13"/>
+      <c r="C22" s="11"/>
+      <c r="D22" s="11"/>
+      <c r="E22" s="11"/>
+      <c r="F22" s="11"/>
+      <c r="G22" s="11"/>
+      <c r="H22" s="12"/>
       <c r="I22"/>
       <c r="J22"/>
       <c r="K22"/>
@@ -1980,12 +1972,12 @@
     <row r="23" spans="1:43" s="6" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="9"/>
       <c r="B23" s="10"/>
-      <c r="C23" s="12"/>
-      <c r="D23" s="12"/>
-      <c r="E23" s="12"/>
-      <c r="F23" s="12"/>
-      <c r="G23" s="12"/>
-      <c r="H23" s="13"/>
+      <c r="C23" s="11"/>
+      <c r="D23" s="11"/>
+      <c r="E23" s="11"/>
+      <c r="F23" s="11"/>
+      <c r="G23" s="11"/>
+      <c r="H23" s="12"/>
       <c r="I23"/>
       <c r="J23"/>
       <c r="K23"/>
@@ -2025,12 +2017,12 @@
     <row r="24" spans="1:43" s="6" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="9"/>
       <c r="B24" s="10"/>
-      <c r="C24" s="12"/>
-      <c r="D24" s="12"/>
-      <c r="E24" s="12"/>
-      <c r="F24" s="12"/>
-      <c r="G24" s="12"/>
-      <c r="H24" s="13"/>
+      <c r="C24" s="11"/>
+      <c r="D24" s="11"/>
+      <c r="E24" s="11"/>
+      <c r="F24" s="11"/>
+      <c r="G24" s="11"/>
+      <c r="H24" s="12"/>
       <c r="I24"/>
       <c r="J24"/>
       <c r="K24"/>
@@ -2070,12 +2062,12 @@
     <row r="25" spans="1:43" s="6" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="9"/>
       <c r="B25" s="10"/>
-      <c r="C25" s="12"/>
-      <c r="D25" s="12"/>
-      <c r="E25" s="12"/>
-      <c r="F25" s="12"/>
-      <c r="G25" s="12"/>
-      <c r="H25" s="13"/>
+      <c r="C25" s="11"/>
+      <c r="D25" s="11"/>
+      <c r="E25" s="11"/>
+      <c r="F25" s="11"/>
+      <c r="G25" s="11"/>
+      <c r="H25" s="12"/>
       <c r="I25"/>
       <c r="J25"/>
       <c r="K25"/>
@@ -2112,15 +2104,17 @@
       <c r="AP25"/>
       <c r="AQ25"/>
     </row>
-    <row r="26" spans="1:43" s="6" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="9"/>
-      <c r="B26" s="10"/>
-      <c r="C26" s="12"/>
-      <c r="D26" s="12"/>
-      <c r="E26" s="12"/>
-      <c r="F26" s="12"/>
-      <c r="G26" s="12"/>
-      <c r="H26" s="13"/>
+    <row r="26" spans="1:43" s="6" customFormat="1" ht="18" x14ac:dyDescent="0.2">
+      <c r="A26" s="26" t="s">
+        <v>22</v>
+      </c>
+      <c r="B26" s="27"/>
+      <c r="C26" s="27"/>
+      <c r="D26" s="27"/>
+      <c r="E26" s="27"/>
+      <c r="F26" s="27"/>
+      <c r="G26" s="27"/>
+      <c r="H26" s="28"/>
       <c r="I26"/>
       <c r="J26"/>
       <c r="K26"/>
@@ -2157,17 +2151,23 @@
       <c r="AP26"/>
       <c r="AQ26"/>
     </row>
-    <row r="27" spans="1:43" s="6" customFormat="1" ht="18" x14ac:dyDescent="0.2">
-      <c r="A27" s="33" t="s">
-        <v>22</v>
-      </c>
-      <c r="B27" s="34"/>
-      <c r="C27" s="34"/>
-      <c r="D27" s="34"/>
-      <c r="E27" s="34"/>
-      <c r="F27" s="34"/>
-      <c r="G27" s="34"/>
-      <c r="H27" s="35"/>
+    <row r="27" spans="1:43" s="6" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A27" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="B27" s="10">
+        <v>2026</v>
+      </c>
+      <c r="C27" s="21" t="s">
+        <v>36</v>
+      </c>
+      <c r="D27" s="11"/>
+      <c r="E27" s="11"/>
+      <c r="F27" s="21"/>
+      <c r="G27" s="21" t="s">
+        <v>36</v>
+      </c>
+      <c r="H27" s="12"/>
       <c r="I27"/>
       <c r="J27"/>
       <c r="K27"/>
@@ -2205,22 +2205,14 @@
       <c r="AQ27"/>
     </row>
     <row r="28" spans="1:43" s="6" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="B28" s="10">
-        <v>2026</v>
-      </c>
-      <c r="C28" s="22" t="s">
-        <v>36</v>
-      </c>
-      <c r="D28" s="12"/>
-      <c r="E28" s="12"/>
-      <c r="F28" s="22"/>
-      <c r="G28" s="22" t="s">
-        <v>36</v>
-      </c>
-      <c r="H28" s="13"/>
+      <c r="A28" s="9"/>
+      <c r="B28" s="10"/>
+      <c r="C28" s="11"/>
+      <c r="D28" s="11"/>
+      <c r="E28" s="11"/>
+      <c r="F28" s="11"/>
+      <c r="G28" s="11"/>
+      <c r="H28" s="12"/>
       <c r="I28"/>
       <c r="J28"/>
       <c r="K28"/>
@@ -2260,12 +2252,12 @@
     <row r="29" spans="1:43" s="6" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="9"/>
       <c r="B29" s="10"/>
-      <c r="C29" s="12"/>
-      <c r="D29" s="12"/>
-      <c r="E29" s="12"/>
-      <c r="F29" s="12"/>
-      <c r="G29" s="12"/>
-      <c r="H29" s="13"/>
+      <c r="C29" s="11"/>
+      <c r="D29" s="11"/>
+      <c r="E29" s="11"/>
+      <c r="F29" s="11"/>
+      <c r="G29" s="11"/>
+      <c r="H29" s="12"/>
       <c r="I29"/>
       <c r="J29"/>
       <c r="K29"/>
@@ -2305,12 +2297,12 @@
     <row r="30" spans="1:43" s="6" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="9"/>
       <c r="B30" s="10"/>
-      <c r="C30" s="12"/>
-      <c r="D30" s="12"/>
-      <c r="E30" s="12"/>
-      <c r="F30" s="12"/>
-      <c r="G30" s="12"/>
-      <c r="H30" s="13"/>
+      <c r="C30" s="11"/>
+      <c r="D30" s="11"/>
+      <c r="E30" s="11"/>
+      <c r="F30" s="11"/>
+      <c r="G30" s="11"/>
+      <c r="H30" s="12"/>
       <c r="I30"/>
       <c r="J30"/>
       <c r="K30"/>
@@ -2350,12 +2342,12 @@
     <row r="31" spans="1:43" s="6" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="9"/>
       <c r="B31" s="10"/>
-      <c r="C31" s="12"/>
-      <c r="D31" s="12"/>
-      <c r="E31" s="12"/>
-      <c r="F31" s="12"/>
-      <c r="G31" s="12"/>
-      <c r="H31" s="13"/>
+      <c r="C31" s="11"/>
+      <c r="D31" s="11"/>
+      <c r="E31" s="11"/>
+      <c r="F31" s="11"/>
+      <c r="G31" s="11"/>
+      <c r="H31" s="12"/>
       <c r="I31"/>
       <c r="J31"/>
       <c r="K31"/>
@@ -2395,12 +2387,12 @@
     <row r="32" spans="1:43" s="6" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="9"/>
       <c r="B32" s="10"/>
-      <c r="C32" s="12"/>
-      <c r="D32" s="12"/>
-      <c r="E32" s="12"/>
-      <c r="F32" s="12"/>
-      <c r="G32" s="12"/>
-      <c r="H32" s="13"/>
+      <c r="C32" s="11"/>
+      <c r="D32" s="11"/>
+      <c r="E32" s="11"/>
+      <c r="F32" s="11"/>
+      <c r="G32" s="11"/>
+      <c r="H32" s="12"/>
       <c r="I32"/>
       <c r="J32"/>
       <c r="K32"/>
@@ -2438,14 +2430,14 @@
       <c r="AQ32"/>
     </row>
     <row r="33" spans="1:43" s="6" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="9"/>
-      <c r="B33" s="10"/>
-      <c r="C33" s="12"/>
-      <c r="D33" s="12"/>
-      <c r="E33" s="12"/>
-      <c r="F33" s="12"/>
-      <c r="G33" s="12"/>
-      <c r="H33" s="13"/>
+      <c r="A33" s="13"/>
+      <c r="B33" s="14"/>
+      <c r="C33" s="15"/>
+      <c r="D33" s="15"/>
+      <c r="E33" s="15"/>
+      <c r="F33" s="15"/>
+      <c r="G33" s="15"/>
+      <c r="H33" s="16"/>
       <c r="I33"/>
       <c r="J33"/>
       <c r="K33"/>
@@ -2482,15 +2474,15 @@
       <c r="AP33"/>
       <c r="AQ33"/>
     </row>
-    <row r="34" spans="1:43" s="6" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="14"/>
-      <c r="B34" s="15"/>
-      <c r="C34" s="16"/>
-      <c r="D34" s="16"/>
-      <c r="E34" s="16"/>
-      <c r="F34" s="16"/>
-      <c r="G34" s="16"/>
-      <c r="H34" s="17"/>
+    <row r="34" spans="1:43" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+      <c r="A34" s="17"/>
+      <c r="B34" s="18"/>
+      <c r="C34" s="19"/>
+      <c r="D34" s="19"/>
+      <c r="E34" s="19"/>
+      <c r="F34" s="19"/>
+      <c r="G34" s="19"/>
+      <c r="H34" s="19"/>
       <c r="I34"/>
       <c r="J34"/>
       <c r="K34"/>
@@ -2527,51 +2519,7 @@
       <c r="AP34"/>
       <c r="AQ34"/>
     </row>
-    <row r="35" spans="1:43" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
-      <c r="A35" s="18"/>
-      <c r="B35" s="19"/>
-      <c r="C35" s="20"/>
-      <c r="D35" s="20"/>
-      <c r="E35" s="20"/>
-      <c r="F35" s="20"/>
-      <c r="G35" s="20"/>
-      <c r="H35" s="20"/>
-      <c r="I35"/>
-      <c r="J35"/>
-      <c r="K35"/>
-      <c r="L35"/>
-      <c r="M35"/>
-      <c r="N35"/>
-      <c r="O35"/>
-      <c r="P35"/>
-      <c r="Q35"/>
-      <c r="R35"/>
-      <c r="S35"/>
-      <c r="T35"/>
-      <c r="U35"/>
-      <c r="V35"/>
-      <c r="W35"/>
-      <c r="X35"/>
-      <c r="Y35"/>
-      <c r="Z35"/>
-      <c r="AA35"/>
-      <c r="AB35"/>
-      <c r="AC35"/>
-      <c r="AD35"/>
-      <c r="AE35"/>
-      <c r="AF35"/>
-      <c r="AG35"/>
-      <c r="AH35"/>
-      <c r="AI35"/>
-      <c r="AJ35"/>
-      <c r="AK35"/>
-      <c r="AL35"/>
-      <c r="AM35"/>
-      <c r="AN35"/>
-      <c r="AO35"/>
-      <c r="AP35"/>
-      <c r="AQ35"/>
-    </row>
+    <row r="35" spans="1:43" customFormat="1" x14ac:dyDescent="0.2"/>
     <row r="36" spans="1:43" customFormat="1" x14ac:dyDescent="0.2"/>
     <row r="37" spans="1:43" customFormat="1" x14ac:dyDescent="0.2"/>
     <row r="38" spans="1:43" customFormat="1" x14ac:dyDescent="0.2"/>
@@ -2617,21 +2565,20 @@
     <row r="78" customFormat="1" x14ac:dyDescent="0.2"/>
     <row r="79" customFormat="1" x14ac:dyDescent="0.2"/>
     <row r="80" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="81" customFormat="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="A19:H19"/>
-    <mergeCell ref="A27:H27"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="F3:H3"/>
+    <mergeCell ref="A18:H18"/>
+    <mergeCell ref="A26:H26"/>
     <mergeCell ref="A4:E4"/>
     <mergeCell ref="A5:H5"/>
     <mergeCell ref="A6:A7"/>
     <mergeCell ref="B6:B7"/>
     <mergeCell ref="A8:H8"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="G1:H1"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A3:E3"/>
-    <mergeCell ref="F3:H3"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.19685039370078738" right="0.19685039370078738" top="0.19685039370078738" bottom="0.19685039370078738" header="0.51181102362204722" footer="0.51181102362204722"/>
@@ -2640,6 +2587,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="c944753b-810f-46c8-bac0-e8d58c60cb9e">
@@ -2647,15 +2603,6 @@
     </lcf76f155ced4ddcb4097134ff3c332f>
   </documentManagement>
 </p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2876,19 +2823,19 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{494C2B63-1469-46C2-8035-1ACD6A901C28}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2E0DA88B-CC83-4B6A-8FB8-D09E146481DE}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <ds:schemaRef ds:uri="c944753b-810f-46c8-bac0-e8d58c60cb9e"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{494C2B63-1469-46C2-8035-1ACD6A901C28}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
